--- a/files/九龙-茶果岭、油塘及鲤鱼门-海傲湾.xlsx
+++ b/files/九龙-茶果岭、油塘及鲤鱼门-海傲湾.xlsx
@@ -8,6 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-B座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +44,91 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +139,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +204,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +220,57 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +647,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -30261,4 +30434,6136 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1-A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 301呎 (1房)
+$791万
+$26,286/呎
+(20年-07月)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 301呎 (1房)
+$784万
+$26,053/呎
+(20年-07月)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$736万
+$27,879/呎
+(19年-06月)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 391呎 (2房)
+$1000万
+$25,575/呎
+(22年-03月)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 295呎 (1房)
+$698万
+$23,644/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 265呎 (1房)
+$592万
+$22,336/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>G | 201呎 (开放式)
+$451万
+$22,438/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>H | 262呎 (1房)
+$580万
+$22,130/呎
+(19年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 301呎 (1房)
+$785万
+$26,073/呎
+(19年-08月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 301呎 (1房)
+$778万
+$25,850/呎
+(20年-06月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$680万
+$25,761/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 391呎 (2房)
+$1000万
+$25,575/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 295呎 (1房)
+$692万
+$23,458/呎
+(20年-07月)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 265呎 (1房)
+$585万
+$22,075/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 201呎 (开放式)
+$449万
+$22,338/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>H | 262呎 (1房)
+$575万
+$21,962/呎
+(19年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 301呎 (1房)
+$779万
+$25,870/呎
+(20年-04月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 301呎 (1房)
+$772万
+$25,648/呎
+(20年-07月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$675万
+$25,561/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 391呎 (2房)
+$1008万
+$25,775/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 295呎 (1房)
+$686万
+$23,271/呎
+(20年-05月)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 265呎 (1房)
+$582万
+$21,981/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 201呎 (开放式)
+$447万
+$22,239/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>H | 262呎 (1房)
+$571万
+$21,790/呎
+(19年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 301呎 (1房)
+$777万
+$25,814/呎
+(20年-03月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 301呎 (1房)
+$766万
+$25,445/呎
+(20年-06月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$664万
+$25,170/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 391呎 (2房)
+$1000万
+$25,573/呎
+(19年-08月)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 295呎 (1房)
+$681万
+$23,088/呎
+(20年-04月)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 265呎 (1房)
+$576万
+$21,736/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 201呎 (开放式)
+$445万
+$22,139/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>H | 262呎 (1房)
+$566万
+$21,622/呎
+(19年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 301呎 (1房)
+$767万
+$25,468/呎
+(20年-04月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 301呎 (1房)
+$760万
+$25,246/呎
+(20年-04月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$659万
+$24,970/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 391呎 (2房)
+$992万
+$25,368/呎
+(20年-05月)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 295呎 (1房)
+$676万
+$22,902/呎
+(19年-12月)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$574万
+$21,560/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>G | 201呎 (开放式)
+$442万
+$21,990/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>H | 262呎 (1房)
+$560万
+$21,374/呎
+(19年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 301呎 (1房)
+$760万
+$25,266/呎
+(21年-04月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 301呎 (1房)
+$754万
+$25,043/呎
+(20年-04月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$654万
+$24,769/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 391呎 (2房)
+$984万
+$25,166/呎
+(20年-07月)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 295呎 (1房)
+$670万
+$22,715/呎
+(19年-11月)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$567万
+$21,316/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>G | 201呎 (开放式)
+$440万
+$21,891/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>H | 262呎 (1房)
+$556万
+$21,206/呎
+(19年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 301呎 (1房)
+$754万
+$25,063/呎
+(21年-04月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 301呎 (1房)
+$748万
+$24,841/呎
+(20年-04月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$649万
+$24,572/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 391呎 (2房)
+$976万
+$24,962/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 295呎 (1房)
+$665万
+$22,539/呎
+(19年-11月)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>F | 265呎 (1房)
+$562万
+$21,223/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>G | 201呎 (开放式)
+$438万
+$21,791/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>H | 262呎 (1房)
+$551万
+$21,034/呎
+(19年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 301呎 (1房)
+$748万
+$24,860/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 301呎 (1房)
+$742万
+$24,648/呎
+(19年-12月)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$644万
+$24,379/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 391呎 (2房)
+$968万
+$24,770/呎
+(20年-10月)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 295呎 (1房)
+$660万
+$22,366/呎
+(19年-11月)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$558万
+$20,974/呎
+(18年-12月)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>G | 201呎 (开放式)
+$436万
+$21,692/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>H | 262呎 (1房)
+$547万
+$20,863/呎
+(18年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 301呎 (1房)
+$742万
+$24,668/呎
+(19年-12月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 301呎 (1房)
+$736万
+$24,455/呎
+(19年-11月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$639万
+$24,189/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 391呎 (2房)
+$947万
+$24,215/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 295呎 (1房)
+$655万
+$22,190/呎
+(19年-10月)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$553万
+$20,805/呎
+(18年-12月)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>G | 201呎 (开放式)
+$434万
+$21,592/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>H | 262呎 (1房)
+$542万
+$20,706/呎
+(19年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 301呎 (1房)
+$737万
+$24,478/呎
+(19年-11月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 301呎 (1房)
+$730万
+$24,266/呎
+(19年-08月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$632万
+$23,924/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 391呎 (2房)
+$953万
+$24,384/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 295呎 (1房)
+$650万
+$22,017/呎
+(19年-11月)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 265呎 (1房)
+$549万
+$20,721/呎
+(18年-12月)</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>G | 201呎 (开放式)
+$432万
+$21,493/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>H | 262呎 (1房)
+$538万
+$20,546/呎
+(19年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 301呎 (1房)
+$731万
+$24,286/呎
+(19年-07月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 301呎 (1房)
+$725万
+$24,073/呎
+(19年-09月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$641万
+$24,269/呎
+(18年-11月)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 391呎 (2房)
+$953万
+$24,366/呎
+(18年-11月)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 295呎 (1房)
+$644万
+$21,841/呎
+(19年-07月)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$545万
+$20,485/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>G | 201呎 (开放式)
+$430万
+$21,393/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t>H | 262呎 (1房)
+$534万
+$20,385/呎
+(19年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 301呎 (1房)
+$725万
+$24,093/呎
+(19年-07月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 301呎 (1房)
+$719万
+$23,880/呎
+(19年-07月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$622万
+$23,545/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 391呎 (2房)
+$945万
+$24,174/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 295呎 (1房)
+$639万
+$21,664/呎
+(19年-06月)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$541万
+$20,323/呎
+(18年-11月)</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>G | 201呎 (开放式)
+$428万
+$21,294/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t>H | 262呎 (1房)
+$530万
+$20,225/呎
+(18年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 301呎 (1房)
+$719万
+$23,900/呎
+(19年-07月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 301呎 (1房)
+$713万
+$23,688/呎
+(19年-06月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$617万
+$23,356/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 391呎 (2房)
+$919万
+$23,504/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 295呎 (1房)
+$634万
+$21,492/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$536万
+$20,165/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>G | 201呎 (开放式)
+$426万
+$21,194/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>H | 262呎 (1房)
+$538万
+$20,515/呎
+(18年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 301呎 (1房)
+$714万
+$23,708/呎
+(19年-07月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 301呎 (1房)
+$707万
+$23,498/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$612万
+$23,163/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 391呎 (2房)
+$923万
+$23,614/呎
+(20年-05月)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 295呎 (1房)
+$618万
+$20,932/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$532万
+$20,004/呎
+(18年-11月)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>G | 201呎 (开放式)
+$409万
+$20,348/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr">
+        <is>
+          <t>H | 262呎 (1房)
+$522万
+$19,905/呎
+(18年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 301呎 (1房)
+$708万
+$23,518/呎
+(19年-06月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 301呎 (1房)
+$702万
+$23,306/呎
+(19年-06月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$600万
+$22,723/呎
+(19年-02月)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 425呎 (2房)
+$995万
+$23,419/呎
+(20年-07月)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 295呎 (1房)
+$608万
+$20,603/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$528万
+$19,846/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>G | 201呎 (开放式)
+$408万
+$20,299/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>H | 262呎 (1房)
+$517万
+$19,744/呎
+(18年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 301呎 (1房)
+$702万
+$23,326/呎
+(19年-06月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 301呎 (1房)
+$696万
+$23,123/呎
+(19年-06月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 264呎 (1房)
+$600万
+$22,727/呎
+(18年-11月)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 425呎 (2房)
+$988万
+$23,238/呎
+(19年-11月)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 295呎 (1房)
+$600万
+$20,339/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$524万
+$19,684/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>G | 201呎 (开放式)
+$407万
+$20,249/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t>H | 262呎 (1房)
+$536万
+$20,462/呎
+(18年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 301呎 (1房)
+$697万
+$23,146/呎
+(19年-06月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 301呎 (1房)
+$690万
+$22,940/呎
+(19年-07月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 290呎 (1房)
+$664万
+$22,890/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 425呎 (2房)
+$980万
+$23,054/呎
+(21年-01月)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 295呎 (1房)
+$598万
+$20,281/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$519万
+$19,523/呎
+(18年-11月)</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>G | 201呎 (开放式)
+$406万
+$20,199/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr">
+        <is>
+          <t>H | 262呎 (1房)
+$509万
+$19,424/呎
+(18年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 301呎 (1房)
+$696万
+$23,133/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 301呎 (1房)
+$690万
+$22,934/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 289呎 (1房)
+$651万
+$22,516/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 425呎 (2房)
+$972万
+$22,871/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 295呎 (1房)
+$592万
+$20,054/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>F | 265呎 (1房)
+$515万
+$19,438/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>G | 201呎 (开放式)
+$405万
+$20,139/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="I22" s="20" t="inlineStr">
+        <is>
+          <t>H | 262呎 (1房)
+$505万
+$19,275/呎
+(18年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 301呎 (1房)
+$681万
+$22,621/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 301呎 (1房)
+$685万
+$22,754/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 289呎 (1房)
+$643万
+$22,263/呎
+(19年-02月)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 425呎 (2房)
+$964万
+$22,689/呎
+(21年-01月)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 295呎 (1房)
+$589万
+$19,963/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>F | 265呎 (1房)
+$511万
+$19,287/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>G | 201呎 (开放式)
+$404万
+$20,090/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="I23" s="20" t="inlineStr">
+        <is>
+          <t>H | 262呎 (1房)
+$501万
+$19,126/呎
+(18年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 301呎 (1房)
+$678万
+$22,508/呎
+(19年-06月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 301呎 (1房)
+$667万
+$22,150/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 290呎 (1房)
+$636万
+$21,917/呎
+(18年-11月)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 425呎 (2房)
+$939万
+$22,085/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 295呎 (1房)
+$582万
+$19,722/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$505万
+$18,985/呎
+(18年-12月)</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>G | 201呎 (开放式)
+$403万
+$20,040/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr">
+        <is>
+          <t>H | 262呎 (1房)
+$495万
+$18,893/呎
+(18年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 301呎 (1房)
+$665万
+$22,106/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 301呎 (1房)
+$659万
+$21,904/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 290呎 (1房)
+$632万
+$21,810/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>D | 425呎 (2房)
+$945万
+$22,233/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 295呎 (1房)
+$575万
+$19,495/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>F | 265呎 (1房)
+$512万
+$19,328/呎
+(18年-11月)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>G | 201呎 (开放式)
+$402万
+$19,990/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
+        <is>
+          <t>H | 262呎 (1房)
+$491万
+$18,744/呎
+(18年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 301呎 (1房)
+$662万
+$21,990/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 301呎 (1房)
+$654万
+$21,734/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 289呎 (1房)
+$628万
+$21,716/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 425呎 (2房)
+$926万
+$21,781/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>E | 295呎 (1房)
+$572万
+$19,403/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$508万
+$19,105/呎
+(18年-11月)</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>G | 201呎 (开放式)
+$401万
+$19,940/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="I26" s="20" t="inlineStr">
+        <is>
+          <t>H | 262呎 (1房)
+$487万
+$18,595/呎
+(18年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 264呎 (1房)
+$666万
+$25,246/呎
+(19年-06月)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 264呎 (1房)
+$638万
+$24,152/呎
+(19年-06月)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 242呎 (1房)
+$698万
+$28,843/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 353呎 (2房)
+$863万
+$24,448/呎
+(20年-04月)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>E | 295呎 (1房)
+$600万
+$20,339/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>F | 244呎 (1房)
+$598万
+$24,508/呎
+(19年-06月)</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>G | 180呎 (开放式)
+$480万
+$26,667/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr">
+        <is>
+          <t>H | 240呎 (1房)
+$590万
+$24,583/呎
+(19年-06月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1-B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 358呎 (2房)
+$1023万
+$28,575/呎
+(20年-10月)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 270呎 (1房)
+$717万
+$26,559/呎
+(19年-06月)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 260呎 (1房)
+$696万
+$26,765/呎
+(19年-06月)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 378呎 (2房)
+$1007万
+$26,638/呎
+(19年-06月)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 264呎 (1房)
+$768万
+$29,076/呎
+(19年-06月)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$645万
+$22,396/呎
+(19年-09月)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>G | 275呎 (1房)
+$597万
+$21,705/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$637万
+$22,498/呎
+(19年-07月)</t>
+        </is>
+      </c>
+      <c r="J5" s="20" t="inlineStr">
+        <is>
+          <t>J | 278呎 (1房)
+$722万
+$25,986/呎
+(19年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 358呎 (2房)
+$944万
+$26,372/呎
+(19年-06月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 269呎 (1房)
+$696万
+$25,862/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 260呎 (1房)
+$680万
+$26,165/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 378呎 (2房)
+$999万
+$26,423/呎
+(21年-04月)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 264呎 (1房)
+$700万
+$26,519/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 287呎 (1房)
+$600万
+$20,906/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 275呎 (1房)
+$592万
+$21,538/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$600万
+$21,201/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>J | 278呎 (1房)
+$676万
+$24,335/呎
+(19年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 358呎 (2房)
+$916万
+$25,575/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 270呎 (1房)
+$688万
+$25,485/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 260呎 (1房)
+$673万
+$25,885/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 378呎 (2房)
+$991万
+$26,212/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 264呎 (1房)
+$695万
+$26,311/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 287呎 (1房)
+$600万
+$20,906/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$588万
+$21,445/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$600万
+$21,201/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>J | 278呎 (1房)
+$669万
+$24,065/呎
+(19年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 358呎 (2房)
+$899万
+$25,112/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 270呎 (1房)
+$676万
+$25,030/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 260呎 (1房)
+$663万
+$25,496/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 378呎 (2房)
+$971万
+$25,677/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 264呎 (1房)
+$684万
+$25,909/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$600万
+$20,833/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 275呎 (1房)
+$583万
+$21,196/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$600万
+$21,201/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>J | 278呎 (1房)
+$650万
+$23,367/呎
+(19年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 358呎 (2房)
+$890万
+$24,860/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 269呎 (1房)
+$669万
+$24,874/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 260呎 (1房)
+$649万
+$24,977/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 378呎 (2房)
+$975万
+$25,804/呎
+(20年-05月)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 264呎 (1房)
+$679万
+$25,712/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$600万
+$20,833/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$578万
+$21,102/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$600万
+$21,201/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>J | 278呎 (1房)
+$655万
+$23,572/呎
+(19年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 358呎 (2房)
+$881万
+$24,620/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 269呎 (1房)
+$662万
+$24,628/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 261呎 (1房)
+$643万
+$24,640/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 378呎 (2房)
+$968万
+$25,603/呎
+(20年-07月)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 264呎 (1房)
+$674万
+$25,511/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$600万
+$20,833/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$574万
+$20,934/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$596万
+$21,064/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>J | 278呎 (1房)
+$637万
+$22,906/呎
+(19年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 358呎 (2房)
+$894万
+$24,966/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 269呎 (1房)
+$656万
+$24,390/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 260呎 (1房)
+$637万
+$24,496/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 378呎 (2房)
+$960万
+$25,399/呎
+(20年-10月)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 264呎 (1房)
+$668万
+$25,311/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$599万
+$20,795/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$569万
+$20,774/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$591万
+$20,894/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>J | 278呎 (1房)
+$631万
+$22,687/呎
+(19年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 358呎 (2房)
+$864万
+$24,140/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 270呎 (1房)
+$650万
+$24,059/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 260呎 (1房)
+$631万
+$24,254/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 378呎 (2房)
+$952万
+$25,196/呎
+(20年-07月)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 264呎 (1房)
+$663万
+$25,110/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>F | 287呎 (1房)
+$594万
+$20,707/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$563万
+$20,540/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$587万
+$20,735/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t>J | 278呎 (1房)
+$620万
+$22,288/呎
+(19年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 358呎 (2房)
+$857万
+$23,930/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 270呎 (1房)
+$644万
+$23,848/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 261呎 (1房)
+$625万
+$23,950/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 378呎 (2房)
+$945万
+$24,992/呎
+(19年-07月)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 264呎 (1房)
+$658万
+$24,909/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$590万
+$20,472/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$558万
+$20,380/呎
+(19年-02月)</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$580万
+$20,505/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="J13" s="20" t="inlineStr">
+        <is>
+          <t>J | 278呎 (1房)
+$614万
+$22,086/呎
+(19年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 358呎 (2房)
+$849万
+$23,721/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 269呎 (1房)
+$638万
+$23,729/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 261呎 (1房)
+$620万
+$23,739/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 378呎 (2房)
+$938万
+$24,802/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 264呎 (1房)
+$650万
+$24,636/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$585万
+$20,316/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$554万
+$20,219/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$576万
+$20,343/呎
+(19年-02月)</t>
+        </is>
+      </c>
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t>J | 278呎 (1房)
+$608万
+$21,888/呎
+(19年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 358呎 (2房)
+$842万
+$23,511/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 269呎 (1房)
+$633万
+$23,517/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 261呎 (1房)
+$614万
+$23,533/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 378呎 (2房)
+$916万
+$24,243/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 264呎 (1房)
+$645万
+$24,447/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$578万
+$20,083/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>G | 275呎 (1房)
+$550万
+$19,985/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$571万
+$20,184/呎
+(19年-02月)</t>
+        </is>
+      </c>
+      <c r="J15" s="20" t="inlineStr">
+        <is>
+          <t>J | 278呎 (1房)
+$603万
+$21,698/呎
+(19年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 358呎 (2房)
+$834万
+$23,302/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 269呎 (1房)
+$627万
+$23,305/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 261呎 (1房)
+$609万
+$23,322/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 378呎 (2房)
+$909万
+$24,053/呎
+(19年-02月)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 264呎 (1房)
+$642万
+$24,330/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$574万
+$19,924/呎
+(19年-02月)</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>G | 275呎 (1房)
+$545万
+$19,825/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$567万
+$20,025/呎
+(19年-02月)</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>J | 278呎 (1房)
+$596万
+$21,435/呎
+(19年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 358呎 (2房)
+$827万
+$23,109/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 269呎 (1房)
+$623万
+$23,160/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 260呎 (1房)
+$604万
+$23,219/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 378呎 (2房)
+$904万
+$23,918/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 264呎 (1房)
+$635万
+$24,064/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 287呎 (1房)
+$569万
+$19,833/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$541万
+$19,737/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$587万
+$20,756/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
+        <is>
+          <t>J | 278呎 (1房)
+$592万
+$21,299/呎
+(19年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 358呎 (2房)
+$821万
+$22,930/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 270呎 (1房)
+$617万
+$22,859/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 260呎 (1房)
+$599万
+$23,038/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 378呎 (2房)
+$895万
+$23,675/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 264呎 (1房)
+$632万
+$23,951/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 287呎 (1房)
+$565万
+$19,672/呎
+(18年-11月)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>G | 275呎 (1房)
+$536万
+$19,505/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$558万
+$19,703/呎
+(19年-02月)</t>
+        </is>
+      </c>
+      <c r="J18" s="20" t="inlineStr">
+        <is>
+          <t>J | 278呎 (1房)
+$586万
+$21,094/呎
+(19年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 358呎 (2房)
+$814万
+$22,749/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 269呎 (1房)
+$611万
+$22,725/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 261呎 (1房)
+$592万
+$22,697/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 378呎 (2房)
+$889万
+$23,511/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 264呎 (1房)
+$625万
+$23,686/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$560万
+$19,444/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>G | 275呎 (1房)
+$532万
+$19,345/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$553万
+$19,544/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="J19" s="20" t="inlineStr">
+        <is>
+          <t>J | 278呎 (1房)
+$584万
+$20,996/呎
+(19年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 358呎 (2房)
+$806万
+$22,514/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 270呎 (1房)
+$600万
+$22,222/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 261呎 (1房)
+$588万
+$22,513/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 378呎 (2房)
+$880万
+$23,294/呎
+(18年-12月)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 264呎 (1房)
+$620万
+$23,496/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 287呎 (1房)
+$556万
+$19,362/呎
+(18年-11月)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$528万
+$19,263/呎
+(18年-12月)</t>
+        </is>
+      </c>
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$549万
+$19,385/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="J20" s="20" t="inlineStr">
+        <is>
+          <t>J | 278呎 (1房)
+$579万
+$20,827/呎
+(19年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 358呎 (2房)
+$797万
+$22,263/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 270呎 (1房)
+$599万
+$22,174/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 261呎 (1房)
+$581万
+$22,264/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 378呎 (2房)
+$893万
+$23,622/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 264呎 (1房)
+$615万
+$23,303/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>F | 287呎 (1房)
+$551万
+$19,213/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$524万
+$19,113/呎
+(18年-12月)</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$544万
+$19,233/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="J21" s="20" t="inlineStr">
+        <is>
+          <t>J | 278呎 (1房)
+$573万
+$20,597/呎
+(19年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 358呎 (2房)
+$789万
+$22,031/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 270呎 (1房)
+$591万
+$21,889/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 261呎 (1房)
+$574万
+$22,011/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 378呎 (2房)
+$868万
+$22,976/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 264呎 (1房)
+$610万
+$23,114/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>F | 287呎 (1房)
+$547万
+$19,059/呎
+(18年-12月)</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>G | 275呎 (1房)
+$520万
+$18,895/呎
+(18年-12月)</t>
+        </is>
+      </c>
+      <c r="I22" s="20" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$552万
+$19,512/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="J22" s="20" t="inlineStr">
+        <is>
+          <t>J | 278呎 (1房)
+$563万
+$20,255/呎
+(19年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 358呎 (2房)
+$777万
+$21,696/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 270呎 (1房)
+$584万
+$21,641/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 260呎 (1房)
+$566万
+$21,777/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 378呎 (2房)
+$862万
+$22,796/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 264呎 (1房)
+$600万
+$22,727/呎
+(19年-02月)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$555万
+$19,267/呎
+(18年-12月)</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>G | 275呎 (1房)
+$527万
+$19,167/呎
+(18年-12月)</t>
+        </is>
+      </c>
+      <c r="I23" s="20" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$536万
+$18,933/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="J23" s="20" t="inlineStr">
+        <is>
+          <t>J | 278呎 (1房)
+$558万
+$20,065/呎
+(19年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 358呎 (2房)
+$768万
+$21,461/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 269呎 (1房)
+$577万
+$21,461/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 261呎 (1房)
+$559万
+$21,433/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 378呎 (2房)
+$852万
+$22,526/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 264呎 (1房)
+$600万
+$22,708/呎
+(18年-11月)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$560万
+$19,458/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$509万
+$18,591/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$491万
+$17,353/呎
+(18年-11月)</t>
+        </is>
+      </c>
+      <c r="J24" s="20" t="inlineStr">
+        <is>
+          <t>J | 278呎 (1房)
+$549万
+$19,755/呎
+(19年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 358呎 (2房)
+$763万
+$21,318/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 269呎 (1房)
+$572万
+$21,253/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 260呎 (1房)
+$555万
+$21,346/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 378呎 (2房)
+$845万
+$22,347/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 289呎 (1房)
+$657万
+$22,727/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$532万
+$18,476/呎
+(18年-11月)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$505万
+$18,442/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$525万
+$18,555/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="J25" s="20" t="inlineStr">
+        <is>
+          <t>J | 278呎 (1房)
+$545万
+$19,594/呎
+(19年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 358呎 (2房)
+$757万
+$21,151/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 270呎 (1房)
+$567万
+$21,004/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 261呎 (1房)
+$551万
+$21,096/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 378呎 (2房)
+$838万
+$22,167/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>E | 290呎 (1房)
+$652万
+$22,469/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>F | 288呎 (1房)
+$528万
+$18,323/呎
+(18年-11月)</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>G | 275呎 (1房)
+$501万
+$18,225/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="I26" s="20" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$521万
+$18,406/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="J26" s="20" t="inlineStr">
+        <is>
+          <t>J | 278呎 (1房)
+$540万
+$19,435/呎
+(19年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 338呎 (2房)
+$794万
+$23,497/呎
+(19年-06月)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 246呎 (1房)
+$628万
+$25,528/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 239呎 (1房)
+$618万
+$25,858/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 340呎 (2房)
+$899万
+$26,453/呎
+(20年-04月)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>E | 243呎 (1房)
+$627万
+$25,819/呎
+(19年-06月)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$600万
+$22,556/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$600万
+$21,898/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr">
+        <is>
+          <t>H | 283呎 (1房)
+$600万
+$21,201/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="J27" s="20" t="inlineStr">
+        <is>
+          <t>J | 278呎 (1房)
+$600万
+$21,583/呎
+(19年-06月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 262呎 (1房)
+$669万
+$25,519/呎
+(19年-06月)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 262呎 (1房)
+$662万
+$25,282/呎
+(19年-06月)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 265呎 (1房)
+$664万
+$25,064/呎
+(19年-08月)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 259呎 (1房)
+$739万
+$28,544/呎
+(20年-03月)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 375呎 (2房)
+$890万
+$23,733/呎
+(22年-04月)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 201呎 (开放式)
+$405万
+$20,169/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>G | 209呎 (开放式)
+$408万
+$19,526/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>H | 260呎 (1房)
+$575万
+$22,115/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="J5" s="20" t="inlineStr">
+        <is>
+          <t>J | 291呎 (1房)
+$709万
+$24,364/呎
+(21年-04月)</t>
+        </is>
+      </c>
+      <c r="K5" s="20" t="inlineStr">
+        <is>
+          <t>K | 274呎 (1房)
+$762万
+$27,810/呎
+(20年-05月)</t>
+        </is>
+      </c>
+      <c r="L5" s="20" t="inlineStr">
+        <is>
+          <t>L | 265呎 (1房)
+$680万
+$25,642/呎
+(19年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 262呎 (1房)
+$654万
+$24,962/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 262呎 (1房)
+$655万
+$25,004/呎
+(19年-06月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 265呎 (1房)
+$657万
+$24,796/呎
+(19年-06月)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 259呎 (1房)
+$654万
+$25,239/呎
+(19年-06月)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 375呎 (2房)
+$898万
+$23,933/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 201呎 (开放式)
+$405万
+$20,169/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 209呎 (开放式)
+$406万
+$19,416/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>H | 261呎 (1房)
+$571万
+$21,862/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>J | 291呎 (1房)
+$701万
+$24,096/呎
+(20年-03月)</t>
+        </is>
+      </c>
+      <c r="K6" s="20" t="inlineStr">
+        <is>
+          <t>K | 275呎 (1房)
+$692万
+$25,171/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="L6" s="20" t="inlineStr">
+        <is>
+          <t>L | 265呎 (1房)
+$664万
+$25,075/呎
+(19年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 262呎 (1房)
+$647万
+$24,691/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 262呎 (1房)
+$636万
+$24,282/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 265呎 (1房)
+$650万
+$24,528/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 259呎 (1房)
+$646万
+$24,961/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 375呎 (2房)
+$890万
+$23,744/呎
+(21年-01月)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 201呎 (开放式)
+$403万
+$20,035/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 209呎 (开放式)
+$404万
+$19,306/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>H | 261呎 (1房)
+$566万
+$21,690/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>J | 291呎 (1房)
+$694万
+$23,838/呎
+(20年-04月)</t>
+        </is>
+      </c>
+      <c r="K7" s="20" t="inlineStr">
+        <is>
+          <t>K | 275呎 (1房)
+$685万
+$24,902/呎
+(19年-06月)</t>
+        </is>
+      </c>
+      <c r="L7" s="20" t="inlineStr">
+        <is>
+          <t>L | 265呎 (1房)
+$657万
+$24,808/呎
+(19年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 262呎 (1房)
+$635万
+$24,240/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 262呎 (1房)
+$624万
+$23,809/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 265呎 (1房)
+$636万
+$24,008/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 259呎 (1房)
+$633万
+$24,436/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 375呎 (2房)
+$883万
+$23,549/呎
+(20年-05月)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 201呎 (开放式)
+$401万
+$19,935/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 209呎 (开放式)
+$401万
+$19,191/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>H | 261呎 (1房)
+$562万
+$21,521/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>J | 291呎 (1房)
+$686万
+$23,581/呎
+(20年-04月)</t>
+        </is>
+      </c>
+      <c r="K8" s="20" t="inlineStr">
+        <is>
+          <t>K | 274呎 (1房)
+$667万
+$24,358/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="L8" s="20" t="inlineStr">
+        <is>
+          <t>L | 265呎 (1房)
+$646万
+$24,358/呎
+(19年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 262呎 (1房)
+$624万
+$23,809/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 262呎 (1房)
+$618万
+$23,603/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 265呎 (1房)
+$630万
+$23,777/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 259呎 (1房)
+$618万
+$23,861/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 375呎 (2房)
+$876万
+$23,368/呎
+(21年-02月)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 201呎 (开放式)
+$400万
+$19,915/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>G | 209呎 (开放式)
+$401万
+$19,172/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>H | 261呎 (1房)
+$557万
+$21,352/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>J | 291呎 (1房)
+$679万
+$23,344/呎
+(19年-11月)</t>
+        </is>
+      </c>
+      <c r="K9" s="20" t="inlineStr">
+        <is>
+          <t>K | 275呎 (1房)
+$678万
+$24,673/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="L9" s="20" t="inlineStr">
+        <is>
+          <t>L | 265呎 (1房)
+$634万
+$23,932/呎
+(19年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 262呎 (1房)
+$618万
+$23,580/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 262呎 (1房)
+$600万
+$22,901/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 265呎 (1房)
+$614万
+$23,170/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 259呎 (1房)
+$600万
+$23,166/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 375呎 (2房)
+$870万
+$23,187/呎
+(20年-10月)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 201呎 (开放式)
+$400万
+$19,896/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>G | 209呎 (开放式)
+$400万
+$19,153/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>H | 260呎 (1房)
+$551万
+$21,185/呎
+(19年-02月)</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>J | 291呎 (1房)
+$673万
+$23,117/呎
+(19年-08月)</t>
+        </is>
+      </c>
+      <c r="K10" s="20" t="inlineStr">
+        <is>
+          <t>K | 274呎 (1房)
+$654万
+$23,872/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="L10" s="20" t="inlineStr">
+        <is>
+          <t>L | 265呎 (1房)
+$628万
+$23,691/呎
+(19年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 262呎 (1房)
+$642万
+$24,519/呎
+(19年-12月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 262呎 (1房)
+$600万
+$22,901/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 265呎 (1房)
+$600万
+$22,642/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 259呎 (1房)
+$600万
+$23,166/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 375呎 (2房)
+$863万
+$23,003/呎
+(20年-07月)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>F | 201呎 (开放式)
+$400万
+$19,876/呎
+(18年-11月)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>G | 209呎 (开放式)
+$400万
+$19,134/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>H | 260呎 (1房)
+$546万
+$21,015/呎
+(19年-02月)</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>J | 291呎 (1房)
+$666万
+$22,890/呎
+(19年-07月)</t>
+        </is>
+      </c>
+      <c r="K11" s="20" t="inlineStr">
+        <is>
+          <t>K | 274呎 (1房)
+$658万
+$24,015/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="L11" s="20" t="inlineStr">
+        <is>
+          <t>L | 265呎 (1房)
+$622万
+$23,460/呎
+(19年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 262呎 (1房)
+$605万
+$23,084/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 262呎 (1房)
+$599万
+$22,874/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 265呎 (1房)
+$600万
+$22,642/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 259呎 (1房)
+$597万
+$23,042/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 374呎 (2房)
+$859万
+$22,971/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>F | 201呎 (开放式)
+$399万
+$19,856/呎
+(18年-11月)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>G | 209呎 (开放式)
+$400万
+$19,115/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>H | 261呎 (1房)
+$542万
+$20,762/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t>J | 291呎 (1房)
+$660万
+$22,663/呎
+(19年-07月)</t>
+        </is>
+      </c>
+      <c r="K12" s="20" t="inlineStr">
+        <is>
+          <t>K | 275呎 (1房)
+$642万
+$23,327/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="L12" s="20" t="inlineStr">
+        <is>
+          <t>L | 265呎 (1房)
+$616万
+$23,230/呎
+(19年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 262呎 (1房)
+$598万
+$22,844/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 262呎 (1房)
+$593万
+$22,634/呎
+(19年-02月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 265呎 (1房)
+$596万
+$22,509/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 259呎 (1房)
+$594万
+$22,923/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 374呎 (2房)
+$838万
+$22,417/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 201呎 (开放式)
+$399万
+$19,836/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>G | 209呎 (开放式)
+$399万
+$19,091/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>H | 260呎 (1房)
+$538万
+$20,685/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="J13" s="20" t="inlineStr">
+        <is>
+          <t>J | 291呎 (1房)
+$646万
+$22,216/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="K13" s="20" t="inlineStr">
+        <is>
+          <t>K | 274呎 (1房)
+$636万
+$23,201/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="L13" s="20" t="inlineStr">
+        <is>
+          <t>L | 265呎 (1房)
+$610万
+$23,023/呎
+(19年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 262呎 (1房)
+$593万
+$22,645/呎
+(19年-02月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 262呎 (1房)
+$590万
+$22,511/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 265呎 (1房)
+$591万
+$22,309/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 259呎 (1房)
+$588万
+$22,722/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 375呎 (2房)
+$839万
+$22,365/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 201呎 (开放式)
+$398万
+$19,816/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>G | 209呎 (开放式)
+$399万
+$19,072/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>H | 261呎 (1房)
+$534万
+$20,444/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t>J | 291呎 (1房)
+$641万
+$22,027/呎
+(19年-06月)</t>
+        </is>
+      </c>
+      <c r="K14" s="20" t="inlineStr">
+        <is>
+          <t>K | 274呎 (1房)
+$630万
+$23,000/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="L14" s="20" t="inlineStr">
+        <is>
+          <t>L | 265呎 (1房)
+$600万
+$22,642/呎
+(19年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 262呎 (1房)
+$588万
+$22,447/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 262呎 (1房)
+$582万
+$22,233/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 265呎 (1房)
+$586万
+$22,109/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 259呎 (1房)
+$583万
+$22,521/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 374呎 (2房)
+$825万
+$22,059/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 201呎 (开放式)
+$398万
+$19,796/呎
+(18年-12月)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>G | 208呎 (开放式)
+$398万
+$19,144/呎
+(18年-12月)</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t>H | 261呎 (1房)
+$529万
+$20,284/呎
+(18年-12月)</t>
+        </is>
+      </c>
+      <c r="J15" s="20" t="inlineStr">
+        <is>
+          <t>J | 291呎 (1房)
+$625万
+$21,491/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="K15" s="20" t="inlineStr">
+        <is>
+          <t>K | 275呎 (1房)
+$625万
+$22,716/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="L15" s="20" t="inlineStr">
+        <is>
+          <t>L | 265呎 (1房)
+$599万
+$22,619/呎
+(19年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 262呎 (1房)
+$583万
+$22,244/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 262呎 (1房)
+$579万
+$22,111/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 265呎 (1房)
+$581万
+$21,909/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 259呎 (1房)
+$578万
+$22,320/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 375呎 (2房)
+$819万
+$21,829/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 201呎 (开放式)
+$398万
+$19,776/呎
+(18年-12月)</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>G | 209呎 (开放式)
+$398万
+$19,033/呎
+(18年-12月)</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t>H | 261呎 (1房)
+$525万
+$20,123/呎
+(18年-12月)</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>J | 291呎 (1房)
+$620万
+$21,302/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="K16" s="20" t="inlineStr">
+        <is>
+          <t>K | 274呎 (1房)
+$619万
+$22,602/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="L16" s="20" t="inlineStr">
+        <is>
+          <t>L | 265呎 (1房)
+$594万
+$22,419/呎
+(19年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 262呎 (1房)
+$578万
+$22,065/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 262呎 (1房)
+$575万
+$21,931/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 265呎 (1房)
+$576万
+$21,740/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 259呎 (1房)
+$574万
+$22,143/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 374呎 (2房)
+$810万
+$21,647/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 201呎 (开放式)
+$397万
+$19,756/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>G | 208呎 (开放式)
+$397万
+$19,106/呎
+(18年-12月)</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>H | 261呎 (1房)
+$521万
+$19,966/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
+        <is>
+          <t>J | 291呎 (1房)
+$615万
+$21,134/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="K17" s="20" t="inlineStr">
+        <is>
+          <t>K | 274呎 (1房)
+$614万
+$22,420/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="L17" s="20" t="inlineStr">
+        <is>
+          <t>L | 265呎 (1房)
+$589万
+$22,242/呎
+(19年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 262呎 (1房)
+$573万
+$21,885/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 262呎 (1房)
+$570万
+$21,763/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 265呎 (1房)
+$572万
+$21,570/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 259呎 (1房)
+$567万
+$21,884/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 375呎 (2房)
+$797万
+$21,256/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 201呎 (开放式)
+$397万
+$19,736/呎
+(18年-11月)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>G | 209呎 (开放式)
+$397万
+$18,995/呎
+(18年-12月)</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr">
+        <is>
+          <t>H | 261呎 (1房)
+$517万
+$19,805/呎
+(18年-12月)</t>
+        </is>
+      </c>
+      <c r="J18" s="20" t="inlineStr">
+        <is>
+          <t>J | 291呎 (1房)
+$610万
+$20,962/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="K18" s="20" t="inlineStr">
+        <is>
+          <t>K | 274呎 (1房)
+$609万
+$22,237/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="L18" s="20" t="inlineStr">
+        <is>
+          <t>L | 265呎 (1房)
+$585万
+$22,060/呎
+(19年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 262呎 (1房)
+$569万
+$21,714/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 262呎 (1房)
+$566万
+$21,592/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 265呎 (1房)
+$567万
+$21,400/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 259呎 (1房)
+$562万
+$21,714/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 375呎 (2房)
+$788万
+$21,005/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 201呎 (开放式)
+$396万
+$19,716/呎
+(18年-12月)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>G | 209呎 (开放式)
+$396万
+$18,971/呎
+(18年-12月)</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>H | 260呎 (1房)
+$513万
+$19,719/呎
+(18年-11月)</t>
+        </is>
+      </c>
+      <c r="J19" s="20" t="inlineStr">
+        <is>
+          <t>J | 291呎 (1房)
+$600万
+$20,619/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="K19" s="20" t="inlineStr">
+        <is>
+          <t>K | 275呎 (1房)
+$599万
+$21,782/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="L19" s="20" t="inlineStr">
+        <is>
+          <t>L | 265呎 (1房)
+$580万
+$21,879/呎
+(19年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 262呎 (1房)
+$563万
+$21,473/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 262呎 (1房)
+$558万
+$21,313/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 265呎 (1房)
+$559万
+$21,094/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 259呎 (1房)
+$558万
+$21,544/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 375呎 (2房)
+$778万
+$20,749/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 201呎 (开放式)
+$396万
+$19,697/呎
+(18年-11月)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>G | 208呎 (开放式)
+$396万
+$19,043/呎
+(18年-12月)</t>
+        </is>
+      </c>
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t>H | 260呎 (1房)
+$508万
+$19,558/呎
+(18年-11月)</t>
+        </is>
+      </c>
+      <c r="J20" s="20" t="inlineStr">
+        <is>
+          <t>J | 291呎 (1房)
+$596万
+$20,495/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="K20" s="20" t="inlineStr">
+        <is>
+          <t>K | 274呎 (1房)
+$596万
+$21,745/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="L20" s="20" t="inlineStr">
+        <is>
+          <t>L | 265呎 (1房)
+$572万
+$21,604/呎
+(19年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 262呎 (1房)
+$555万
+$21,195/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 262呎 (1房)
+$553万
+$21,111/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 265呎 (1房)
+$552万
+$20,823/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 259呎 (1房)
+$554万
+$21,375/呎
+(19年-02月)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 375呎 (2房)
+$772万
+$20,579/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>F | 201呎 (开放式)
+$396万
+$19,677/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>G | 209呎 (开放式)
+$405万
+$19,359/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr">
+        <is>
+          <t>H | 260呎 (1房)
+$504万
+$19,400/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="J21" s="20" t="inlineStr">
+        <is>
+          <t>J | 291呎 (1房)
+$588万
+$20,223/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="K21" s="20" t="inlineStr">
+        <is>
+          <t>K | 275呎 (1房)
+$589万
+$21,422/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="L21" s="20" t="inlineStr">
+        <is>
+          <t>L | 265呎 (1房)
+$566万
+$21,362/呎
+(19年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 262呎 (1房)
+$549万
+$20,962/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 262呎 (1房)
+$544万
+$20,763/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 265呎 (1房)
+$545万
+$20,555/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 259呎 (1房)
+$549万
+$21,205/呎
+(19年-02月)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 375呎 (2房)
+$766万
+$20,419/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>F | 201呎 (开放式)
+$413万
+$20,537/呎
+(18年-11月)</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>G | 209呎 (开放式)
+$395万
+$18,914/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="I22" s="20" t="inlineStr">
+        <is>
+          <t>H | 261呎 (1房)
+$500万
+$19,176/呎
+(18年-12月)</t>
+        </is>
+      </c>
+      <c r="J22" s="20" t="inlineStr">
+        <is>
+          <t>J | 291呎 (1房)
+$583万
+$20,034/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="K22" s="20" t="inlineStr">
+        <is>
+          <t>K | 275呎 (1房)
+$582万
+$21,178/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="L22" s="20" t="inlineStr">
+        <is>
+          <t>L | 265呎 (1房)
+$558万
+$21,045/呎
+(19年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 262呎 (1房)
+$543万
+$20,733/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 262呎 (1房)
+$538万
+$20,534/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 265呎 (1房)
+$540万
+$20,362/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 259呎 (1房)
+$545万
+$21,035/呎
+(19年-02月)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 375呎 (2房)
+$760万
+$20,259/呎
+(19年-02月)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>F | 201呎 (开放式)
+$395万
+$19,637/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>G | 208呎 (开放式)
+$395万
+$18,986/呎
+(18年-12月)</t>
+        </is>
+      </c>
+      <c r="I23" s="20" t="inlineStr">
+        <is>
+          <t>H | 261呎 (1房)
+$496万
+$19,023/呎
+(18年-12月)</t>
+        </is>
+      </c>
+      <c r="J23" s="20" t="inlineStr">
+        <is>
+          <t>J | 291呎 (1房)
+$576万
+$19,780/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="K23" s="20" t="inlineStr">
+        <is>
+          <t>K | 275呎 (1房)
+$576万
+$20,949/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="L23" s="20" t="inlineStr">
+        <is>
+          <t>L | 265呎 (1房)
+$552万
+$20,811/呎
+(19年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 262呎 (1房)
+$536万
+$20,447/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 262呎 (1房)
+$532万
+$20,294/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 265呎 (1房)
+$532万
+$20,083/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 259呎 (1房)
+$538万
+$20,784/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 374呎 (2房)
+$751万
+$20,075/呎
+(18年-12月)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>F | 201呎 (开放式)
+$394万
+$19,617/呎
+(18年-11月)</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>G | 209呎 (开放式)
+$394万
+$18,876/呎
+(18年-11月)</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr">
+        <is>
+          <t>H | 261呎 (1房)
+$502万
+$19,215/呎
+(18年-12月)</t>
+        </is>
+      </c>
+      <c r="J24" s="20" t="inlineStr">
+        <is>
+          <t>J | 291呎 (1房)
+$568万
+$19,505/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="K24" s="20" t="inlineStr">
+        <is>
+          <t>K | 275呎 (1房)
+$569万
+$20,698/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="L24" s="20" t="inlineStr">
+        <is>
+          <t>L | 265呎 (1房)
+$544万
+$20,525/呎
+(19年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 262呎 (1房)
+$532万
+$20,286/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 262呎 (1房)
+$526万
+$20,095/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 265呎 (1房)
+$528万
+$19,925/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 259呎 (1房)
+$534万
+$20,614/呎
+(18年-11月)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 375呎 (2房)
+$745万
+$19,861/呎
+(18年-12月)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>F | 201呎 (开放式)
+$394万
+$19,597/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>G | 209呎 (开放式)
+$394万
+$18,856/呎
+(18年-11月)</t>
+        </is>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
+        <is>
+          <t>H | 260呎 (1房)
+$498万
+$19,135/呎
+(18年-12月)</t>
+        </is>
+      </c>
+      <c r="J25" s="20" t="inlineStr">
+        <is>
+          <t>J | 291呎 (1房)
+$563万
+$19,344/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="K25" s="20" t="inlineStr">
+        <is>
+          <t>K | 275呎 (1房)
+$563万
+$20,465/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="L25" s="20" t="inlineStr">
+        <is>
+          <t>L | 265呎 (1房)
+$540万
+$20,366/呎
+(19年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 262呎 (1房)
+$527万
+$20,126/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 262呎 (1房)
+$522万
+$19,935/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 265呎 (1房)
+$524万
+$19,766/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 259呎 (1房)
+$530万
+$20,456/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>E | 375呎 (2房)
+$739万
+$19,701/呎
+(18年-11月)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>F | 201呎 (开放式)
+$394万
+$19,577/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>G | 209呎 (开放式)
+$394万
+$18,833/呎
+(19年-02月)</t>
+        </is>
+      </c>
+      <c r="I26" s="20" t="inlineStr">
+        <is>
+          <t>H | 261呎 (1房)
+$483万
+$18,494/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="J26" s="20" t="inlineStr">
+        <is>
+          <t>J | 291呎 (1房)
+$561万
+$19,265/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="K26" s="20" t="inlineStr">
+        <is>
+          <t>K | 274呎 (1房)
+$560万
+$20,453/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="L26" s="20" t="inlineStr">
+        <is>
+          <t>L | 265呎 (1房)
+$535万
+$20,204/呎
+(19年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 240呎 (1房)
+$580万
+$24,167/呎
+(19年-06月)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 240呎 (1房)
+$580万
+$24,167/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 243呎 (1房)
+$598万
+$24,609/呎
+(19年-06月)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 238呎 (1房)
+$598万
+$25,126/呎
+(19年-06月)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>E | 375呎 (2房)
+$828万
+$22,080/呎
+(19年-11月)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>F | 180呎 (开放式)
+$480万
+$26,667/呎
+(19年-06月)</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>G | 187呎 (开放式)
+$480万
+$25,668/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr">
+        <is>
+          <t>H | 239呎 (1房)
+$580万
+$24,268/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="J27" s="20" t="inlineStr">
+        <is>
+          <t>J | 269呎 (1房)
+$600万
+$22,305/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="K27" s="20" t="inlineStr">
+        <is>
+          <t>K | 253呎 (1房)
+$590万
+$23,320/呎
+(19年-06月)</t>
+        </is>
+      </c>
+      <c r="L27" s="20" t="inlineStr">
+        <is>
+          <t>L | 243呎 (1房)
+$585万
+$24,074/呎
+(19年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 576呎 (2房)
+$1354万
+$23,500/呎
+(20年-07月)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 493呎 (2房)
+$1208万
+$24,503/呎
+(20年-05月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr"/>
+      <c r="E28" s="22" t="inlineStr"/>
+      <c r="F28" s="22" t="inlineStr"/>
+      <c r="G28" s="22" t="inlineStr"/>
+      <c r="H28" s="22" t="inlineStr"/>
+      <c r="I28" s="22" t="inlineStr"/>
+      <c r="J28" s="22" t="inlineStr"/>
+      <c r="K28" s="22" t="inlineStr"/>
+      <c r="L28" s="22" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-茶果岭、油塘及鲤鱼门-海傲湾.xlsx
+++ b/files/九龙-茶果岭、油塘及鲤鱼门-海傲湾.xlsx
@@ -647,7 +647,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
